--- a/data/trending_integrated_20261012_09.xlsx
+++ b/data/trending_integrated_20261012_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46400</v>
+        <v>45850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="G2" t="n">
-        <v>875</v>
+        <v>967</v>
       </c>
       <c r="H2" t="n">
         <v>13.33</v>
@@ -604,13 +604,13 @@
         <v>47550</v>
       </c>
       <c r="M2" t="n">
-        <v>46200</v>
+        <v>45000</v>
       </c>
       <c r="N2" t="n">
         <v>13.39</v>
       </c>
       <c r="O2" t="n">
-        <v>3048980250</v>
+        <v>11222788550</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 리보세라닙·캄렐리주맙 병용요법 FDA 재신청 공시 확인. 시장은 긍정적 반응 기대.</t>
+          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출 관련 속보 및 긍정적 기대감. 공시 기반 내용.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '재신청', '간암']</t>
+          <t>['FDA', '간암', '재신청']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1643000</v>
+        <v>16700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'+0.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>419</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>289</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>1597</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
-        <v>49.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1681000</v>
+        <v>16670</v>
       </c>
       <c r="K3" t="n">
-        <v>1640000</v>
+        <v>16500</v>
       </c>
       <c r="L3" t="n">
-        <v>1653000</v>
+        <v>16840</v>
       </c>
       <c r="M3" t="n">
-        <v>1640000</v>
+        <v>16420</v>
       </c>
       <c r="N3" t="n">
-        <v>49.59</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>299240176000</v>
+        <v>8194507930</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q3" t="n">
-        <v>403000</v>
+        <v>3320</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇용 D램 수요 증가 기대감과 함께 나스닥 선물 강세 언급. 하지만 솔리다임 쪼개기 상장 등 일부 부정적 내용도 혼재.</t>
+          <t>공매도 및 대차 관련 소액주주연대의 활동 언급. 건설주 하락 출발 및 정치적 이슈 관련 부정적 내용.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['D램', '로봇', '수요']</t>
+          <t>['공매도', '소액주주연대', '건설주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -739,6 +739,190 @@
         </is>
       </c>
       <c r="Z3" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>259750</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'-0.86%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E4" t="n">
+        <v>530</v>
+      </c>
+      <c r="F4" t="n">
+        <v>329</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="H4" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>262000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>260000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>261000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>258500</v>
+      </c>
+      <c r="N4" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="O4" t="n">
+        <v>348245214250</v>
+      </c>
+      <c r="P4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>반도체 주 상승 시작 기대감 및 로봇 D램 관련 긍정 전망. 그러나 실시간 갭 하락 시작 및 부정적 정치/경제 상황 언급.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['반도체', '로봇 D램', 'AI']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1635000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-2.74%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>493</v>
+      </c>
+      <c r="F5" t="n">
+        <v>328</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1697</v>
+      </c>
+      <c r="H5" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1681000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1640000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1653000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="O5" t="n">
+        <v>576611470500</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>로봇용 D램 수요 폭증 호재 및 반도체 관련 긍정 전망. 미국 선물 상승 및 월요일 하락 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['D램', '로봇', '반도체']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261012_09.xlsx
+++ b/data/trending_integrated_20261012_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45850</v>
+        <v>45950</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F2" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G2" t="n">
-        <v>967</v>
+        <v>1208</v>
       </c>
       <c r="H2" t="n">
         <v>13.33</v>
@@ -610,7 +610,7 @@
         <v>13.39</v>
       </c>
       <c r="O2" t="n">
-        <v>11222788550</v>
+        <v>13926191350</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출 관련 속보 및 긍정적 기대감. 공시 기반 내용.</t>
+          <t>HLB 간암 1차 치료제(리보세라닙, 캄렐리주맙 병용요법) FDA 재승인 서류 제출 공시 확인. 연말 30만 기대 및 기관 매수 촉구.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '간암', '재신청']</t>
+          <t>['FDA', '재신청', '공시']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16700</v>
+        <v>16660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="H3" t="n">
         <v>9.470000000000001</v>
@@ -702,7 +702,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8194507930</v>
+        <v>11269316415</v>
       </c>
       <c r="P3" t="n">
         <v>40350</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>공매도 및 대차 관련 소액주주연대의 활동 언급. 건설주 하락 출발 및 정치적 이슈 관련 부정적 내용.</t>
+          <t>대우건설 주주연대의 활동과 범죄짓거리를 멈추자는 내용이 반복적으로 언급됨. 공매도 및 하락 출발에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공매도', '소액주주연대', '건설주']</t>
+          <t>['대차', '소액주주연대', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>259750</v>
+        <v>261000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>530</v>
+        <v>563</v>
       </c>
       <c r="F4" t="n">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>1722</v>
+        <v>1790</v>
       </c>
       <c r="H4" t="n">
         <v>46.35</v>
@@ -794,7 +794,7 @@
         <v>46.38</v>
       </c>
       <c r="O4" t="n">
-        <v>348245214250</v>
+        <v>463947816000</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 주 상승 시작 기대감 및 로봇 D램 관련 긍정 전망. 그러나 실시간 갭 하락 시작 및 부정적 정치/경제 상황 언급.</t>
+          <t>반도체 주 상승 시작 기대감과 함께 로봇 D램 및 낸드 관련 긍정적 전망 제시. 다만, 실시간 갭하락 시작 및 매수 대기 의견도 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '로봇 D램', 'AI']</t>
+          <t>['반도체', '로봇 D램', '낸드']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1635000</v>
+        <v>18470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.74%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>493</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>328</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>1697</v>
+        <v>97</v>
       </c>
       <c r="H5" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K5" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L5" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M5" t="n">
-        <v>1630000</v>
+        <v>18300</v>
       </c>
       <c r="N5" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O5" t="n">
-        <v>576611470500</v>
+        <v>8585882780</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q5" t="n">
-        <v>403000</v>
+        <v>18300</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇용 D램 수요 폭증 호재 및 반도체 관련 긍정 전망. 미국 선물 상승 및 월요일 하락 가능성 언급.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 3분기 어닝쇼크 가능성 및 52주 최저가 경신 등 부정적 전망 제시. 자사주 소각, 배당 공시 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,20 +911,204 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>['LNG', 'FLNG', '수주']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1641500</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-2.35%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>574</v>
+      </c>
+      <c r="F6" t="n">
+        <v>361</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1865</v>
+      </c>
+      <c r="H6" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1681000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1640000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1653000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="O6" t="n">
+        <v>748182600000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>로봇용 D램 수요 폭증 호재 및 반도체 관련 긍정 전망. 미국 선물 상승 및 월요일 하락 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>['D램', '로봇', '반도체']</t>
         </is>
       </c>
-      <c r="X5" t="n">
+      <c r="X6" t="n">
         <v>9</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16550</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-2.47%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" t="n">
+        <v>214</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>16970</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17030</v>
+      </c>
+      <c r="L7" t="n">
+        <v>17400</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16310</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O7" t="n">
+        <v>23450532810</v>
+      </c>
+      <c r="P7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AI 및 광통신 시장 성장률 전망과 함께 미국 광통신 대장주 신고가 언급. 17500원 돌파 여부 및 12000원 지지선 중요성 강조.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '신고가']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>010170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_09.xlsx
+++ b/data/trending_integrated_20261012_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45950</v>
+        <v>46050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.66%</t>
+          <t>'+0.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.06</v>
       </c>
       <c r="E2" t="n">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="F2" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G2" t="n">
-        <v>1208</v>
+        <v>1349</v>
       </c>
       <c r="H2" t="n">
         <v>13.33</v>
@@ -610,7 +610,7 @@
         <v>13.39</v>
       </c>
       <c r="O2" t="n">
-        <v>13926191350</v>
+        <v>15308962025</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -619,23 +619,23 @@
         <v>24150</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-135000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제(리보세라닙, 캄렐리주맙 병용요법) FDA 재승인 서류 제출 공시 확인. 연말 30만 기대 및 기관 매수 촉구.</t>
+          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출 공시 확인. 연말 30만 기대감과 함께 공매도 세력에 대한 강한 비판.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '재신청', '공시']</t>
+          <t>['FDA', '공시', '재승인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="H3" t="n">
         <v>9.470000000000001</v>
@@ -702,7 +702,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>11269316415</v>
+        <v>13260496030</v>
       </c>
       <c r="P3" t="n">
         <v>40350</v>
@@ -711,14 +711,14 @@
         <v>3320</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대우건설 주주연대의 활동과 범죄짓거리를 멈추자는 내용이 반복적으로 언급됨. 공매도 및 하락 출발에 대한 부정적 언급.</t>
+          <t>주주들의 불만과 '천인공노할 범죄짓'에 대한 강한 비판이 반복적으로 제기됨. 대차 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['대차', '소액주주연대', '공매도']</t>
+          <t>['주주', '불만', '대차']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>261000</v>
+        <v>8030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.38%</t>
+          <t>'-1.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>563</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>1790</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>46.35</v>
+        <v>26.37</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>262000</v>
+        <v>8160</v>
       </c>
       <c r="K4" t="n">
-        <v>260000</v>
+        <v>8070</v>
       </c>
       <c r="L4" t="n">
-        <v>261000</v>
+        <v>8110</v>
       </c>
       <c r="M4" t="n">
-        <v>258500</v>
+        <v>7980</v>
       </c>
       <c r="N4" t="n">
-        <v>46.38</v>
+        <v>26.38</v>
       </c>
       <c r="O4" t="n">
-        <v>463947816000</v>
+        <v>4161470540</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q4" t="n">
-        <v>90200</v>
+        <v>7980</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-133000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 주 상승 시작 기대감과 함께 로봇 D램 및 낸드 관련 긍정적 전망 제시. 다만, 실시간 갭하락 시작 및 매수 대기 의견도 존재.</t>
+          <t>미래 전망이 불투명하고 답답하다는 의견이 지배적. 플립 기술 관련 뉴스와 목표가에 대한 회의적 시각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '로봇 D램', '낸드']</t>
+          <t>['미래전망', '플립', '목표가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18470</v>
+        <v>1638000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>631</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>394</v>
       </c>
       <c r="G5" t="n">
-        <v>97</v>
+        <v>1983</v>
       </c>
       <c r="H5" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K5" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L5" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M5" t="n">
-        <v>18300</v>
+        <v>1630000</v>
       </c>
       <c r="N5" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O5" t="n">
-        <v>8585882780</v>
+        <v>901840229000</v>
       </c>
       <c r="P5" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>18300</v>
+        <v>403000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-139000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 3분기 어닝쇼크 가능성 및 52주 최저가 경신 등 부정적 전망 제시. 자사주 소각, 배당 공시 기대.</t>
+          <t>로봇용 D램 수요 20배 폭증 호재 속에서 주가 방향성에 대한 상반된 의견 존재. 긍정적 전망과 폭락 우려 공존.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['LNG', 'FLNG', '수주']</t>
+          <t>['D램', '로봇', '수요']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1641500</v>
+        <v>18360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.35%</t>
+          <t>'-2.65%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>574</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>361</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>1865</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K6" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L6" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M6" t="n">
-        <v>1630000</v>
+        <v>18300</v>
       </c>
       <c r="N6" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O6" t="n">
-        <v>748182600000</v>
+        <v>10547216950</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q6" t="n">
-        <v>403000</v>
+        <v>18300</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇용 D램 수요 폭증 호재 및 반도체 관련 긍정 전망. 미국 선물 상승 및 월요일 하락 가능성 언급.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 52주 신저가 갱신. 3분기 어닝쇼크 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['D램', '로봇', '반도체']</t>
+          <t>['수주', 'LNG', '어닝쇼크']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16550</v>
+        <v>16490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="H7" t="n">
         <v>3.37</v>
@@ -1070,7 +1070,7 @@
         <v>3.97</v>
       </c>
       <c r="O7" t="n">
-        <v>23450532810</v>
+        <v>26406544440</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1079,14 +1079,14 @@
         <v>1272</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 및 광통신 시장 성장률 전망과 함께 미국 광통신 대장주 신고가 언급. 17500원 돌파 여부 및 12000원 지지선 중요성 강조.</t>
+          <t>AI 및 광통신 테마 상승 기대감 속 3만원 예상. 미국 광통신 대장주 신고가 및 20일선 지지선 중요성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '신고가']</t>
+          <t>['광통신', 'AI', '테마']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1109,6 +1109,98 @@
       <c r="Z7" t="inlineStr">
         <is>
           <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>260000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-3.35%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>608</v>
+      </c>
+      <c r="F8" t="n">
+        <v>365</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1897</v>
+      </c>
+      <c r="H8" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>269000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>574348000000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>마이크론 파업 및 AI 관련 긍정적 기대감 속 반도체 주 상승 전망. 다만, 실적 개선에 대한 기대감과 주가 하락세가 공존.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['반도체', 'AI', '실적']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>005930</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_09.xlsx
+++ b/data/trending_integrated_20261012_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46050</v>
+        <v>14240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E2" t="n">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>1349</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
-        <v>13.33</v>
+        <v>0.21</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>45650</v>
+        <v>13910</v>
       </c>
       <c r="K2" t="n">
-        <v>47550</v>
+        <v>13350</v>
       </c>
       <c r="L2" t="n">
-        <v>47550</v>
+        <v>14830</v>
       </c>
       <c r="M2" t="n">
-        <v>45000</v>
+        <v>13350</v>
       </c>
       <c r="N2" t="n">
-        <v>13.39</v>
+        <v>0.09</v>
       </c>
       <c r="O2" t="n">
-        <v>15308962025</v>
+        <v>24648013745</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>28700</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>11600</v>
       </c>
       <c r="R2" t="n">
-        <v>-135000</v>
+        <v>93000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출 공시 확인. 연말 30만 기대감과 함께 공매도 세력에 대한 강한 비판.</t>
+          <t>방산 테마 속 덕산넵코어스의 주가 움직임에 대한 투자자 불만 및 보호예수 관련 우려.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '공시', '재승인']</t>
+          <t>['방산', '보호예수', '테마']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16660</v>
+        <v>16760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H3" t="n">
         <v>9.470000000000001</v>
@@ -693,7 +693,7 @@
         <v>16500</v>
       </c>
       <c r="L3" t="n">
-        <v>16840</v>
+        <v>16870</v>
       </c>
       <c r="M3" t="n">
         <v>16420</v>
@@ -702,7 +702,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>13260496030</v>
+        <v>16165753700</v>
       </c>
       <c r="P3" t="n">
         <v>40350</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>주주들의 불만과 '천인공노할 범죄짓'에 대한 강한 비판이 반복적으로 제기됨. 대차 관련 언급 다수.</t>
+          <t>대우건설 주주연대의 범죄짓 중단 요구와 대차 관련 논쟁.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주주', '불만', '대차']</t>
+          <t>['대차', '주주연대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8030</v>
+        <v>45750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.59%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>1369</v>
       </c>
       <c r="H4" t="n">
-        <v>26.37</v>
+        <v>13.33</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8160</v>
+        <v>45650</v>
       </c>
       <c r="K4" t="n">
-        <v>8070</v>
+        <v>47550</v>
       </c>
       <c r="L4" t="n">
-        <v>8110</v>
+        <v>47550</v>
       </c>
       <c r="M4" t="n">
-        <v>7980</v>
+        <v>45000</v>
       </c>
       <c r="N4" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="O4" t="n">
-        <v>4161470540</v>
+        <v>16524820450</v>
       </c>
       <c r="P4" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>7980</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>-133000</v>
+        <v>-135000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미래 전망이 불투명하고 답답하다는 의견이 지배적. 플립 기술 관련 뉴스와 목표가에 대한 회의적 시각.</t>
+          <t>HLB의 간암 1차 치료제 FDA 재승인 서류 제출 공시 및 이에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['미래전망', '플립', '목표가']</t>
+          <t>['FDA', '재승인', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1638000</v>
+        <v>259000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.56%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="F5" t="n">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="G5" t="n">
-        <v>1983</v>
+        <v>1908</v>
       </c>
       <c r="H5" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K5" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L5" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M5" t="n">
-        <v>1630000</v>
+        <v>258500</v>
       </c>
       <c r="N5" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O5" t="n">
-        <v>901840229000</v>
+        <v>663621164500</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R5" t="n">
-        <v>-139000</v>
+        <v>5000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇용 D램 수요 20배 폭증 호재 속에서 주가 방향성에 대한 상반된 의견 존재. 긍정적 전망과 폭락 우려 공존.</t>
+          <t>마이크론 파업 및 AI 관련 긍정적 기대감 속 반도체 주 상승 전망. 다만, 실적 개선에 대한 기대감과 주가 하락세가 공존.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['D램', '로봇', '수요']</t>
+          <t>['반도체', 'AI', '실적']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18360</v>
+        <v>8000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.65%</t>
+          <t>'-1.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
         <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
-        <v>27.61</v>
+        <v>26.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18860</v>
+        <v>8160</v>
       </c>
       <c r="K6" t="n">
-        <v>18690</v>
+        <v>8070</v>
       </c>
       <c r="L6" t="n">
-        <v>18760</v>
+        <v>8110</v>
       </c>
       <c r="M6" t="n">
-        <v>18300</v>
+        <v>7980</v>
       </c>
       <c r="N6" t="n">
-        <v>27.68</v>
+        <v>26.38</v>
       </c>
       <c r="O6" t="n">
-        <v>10547216950</v>
+        <v>4827130225</v>
       </c>
       <c r="P6" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q6" t="n">
-        <v>18300</v>
+        <v>7980</v>
       </c>
       <c r="R6" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 52주 신저가 갱신. 3분기 어닝쇼크 가능성 언급.</t>
+          <t>LG디스플레이의 FLIP 기술 관련 논의와 미래 전망에 대한 부정적 인식 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['수주', 'LNG', '어닝쇼크']</t>
+          <t>['FLIP', '기술', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16490</v>
+        <v>1638000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.83%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.6</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>660</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>406</v>
       </c>
       <c r="G7" t="n">
-        <v>234</v>
+        <v>2068</v>
       </c>
       <c r="H7" t="n">
-        <v>3.37</v>
+        <v>49.52</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16970</v>
+        <v>1681000</v>
       </c>
       <c r="K7" t="n">
-        <v>17030</v>
+        <v>1640000</v>
       </c>
       <c r="L7" t="n">
-        <v>17400</v>
+        <v>1653000</v>
       </c>
       <c r="M7" t="n">
-        <v>16310</v>
+        <v>1630000</v>
       </c>
       <c r="N7" t="n">
-        <v>3.97</v>
+        <v>49.59</v>
       </c>
       <c r="O7" t="n">
-        <v>26406544440</v>
+        <v>1003442654000</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1272</v>
+        <v>403000</v>
       </c>
       <c r="R7" t="n">
-        <v>-42000</v>
+        <v>-139000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AI 및 광통신 테마 상승 기대감 속 3만원 예상. 미국 광통신 대장주 신고가 및 20일선 지지선 중요성 언급.</t>
+          <t>로봇용 D램 수요 증가 뉴스에도 불구하고 주가 하락 및 투자자 불만.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '테마']</t>
+          <t>['D램', '로봇', '수요']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>260000</v>
+        <v>18370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>608</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>1897</v>
+        <v>108</v>
       </c>
       <c r="H8" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>269000</v>
+        <v>18860</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>18690</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>18760</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="N8" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="O8" t="n">
-        <v>574348000000</v>
+        <v>12221549555</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>마이크론 파업 및 AI 관련 긍정적 기대감 속 반도체 주 상승 전망. 다만, 실적 개선에 대한 기대감과 주가 하락세가 공존.</t>
+          <t>삼성중공업의 수주 소식에도 불구하고 주가 하락 및 신저점 갱신에 대한 불만.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,20 +1187,112 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '실적']</t>
+          <t>['수주', '신저점', '조선주']</t>
         </is>
       </c>
       <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16390</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-3.42%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>255</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>16970</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17030</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17400</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16310</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O9" t="n">
+        <v>29069382045</v>
+      </c>
+      <c r="P9" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-42000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>광통신 테마 부각 속에서 대한광통신의 주가 상승 기대와 관련 뉴스 언급.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '테마']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>9</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>005930</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>010170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_09.xlsx
+++ b/data/trending_integrated_20261012_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14240</v>
+        <v>14710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+5.75%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.12</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
         <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
         <v>0.21</v>
@@ -601,7 +601,7 @@
         <v>13350</v>
       </c>
       <c r="L2" t="n">
-        <v>14830</v>
+        <v>14880</v>
       </c>
       <c r="M2" t="n">
         <v>13350</v>
@@ -610,7 +610,7 @@
         <v>0.09</v>
       </c>
       <c r="O2" t="n">
-        <v>24648013745</v>
+        <v>32129726815</v>
       </c>
       <c r="P2" t="n">
         <v>28700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>방산 테마 속 덕산넵코어스의 주가 움직임에 대한 투자자 불만 및 보호예수 관련 우려.</t>
+          <t>덕산넵코어스의 주가 상승 기대와 기관 매수세 언급. 보호예수 및 투매 우려도 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['방산', '보호예수', '테마']</t>
+          <t>['방산주', '보호예수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16760</v>
+        <v>16640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'-0.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
         <v>9.470000000000001</v>
@@ -702,7 +702,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>16165753700</v>
+        <v>17668812030</v>
       </c>
       <c r="P3" t="n">
         <v>40350</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대우건설 주주연대의 범죄짓 중단 요구와 대차 관련 논쟁.</t>
+          <t>대우건설 주주연대의 활동 촉구 및 가격 상승 기대. 다만, 감정적 표현이 다수.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['대차', '주주연대']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45750</v>
+        <v>45450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'-0.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F4" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G4" t="n">
-        <v>1369</v>
+        <v>1455</v>
       </c>
       <c r="H4" t="n">
         <v>13.33</v>
@@ -794,7 +794,7 @@
         <v>13.39</v>
       </c>
       <c r="O4" t="n">
-        <v>16524820450</v>
+        <v>17811087000</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB의 간암 1차 치료제 FDA 재승인 서류 제출 공시 및 이에 따른 주가 상승 기대감.</t>
+          <t>HLB의 리보세라닙 FDA 재승인 서류 제출에 따른 주가 상승 기대. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA', '재승인', '공시']</t>
+          <t>['리보세라닙', 'FDA', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>259000</v>
+        <v>256500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>635</v>
+        <v>675</v>
       </c>
       <c r="F5" t="n">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G5" t="n">
-        <v>1908</v>
+        <v>1984</v>
       </c>
       <c r="H5" t="n">
         <v>46.35</v>
@@ -880,13 +880,13 @@
         <v>262500</v>
       </c>
       <c r="M5" t="n">
-        <v>258500</v>
+        <v>256000</v>
       </c>
       <c r="N5" t="n">
         <v>46.38</v>
       </c>
       <c r="O5" t="n">
-        <v>663621164500</v>
+        <v>836036119000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8000</v>
+        <v>18330</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H6" t="n">
-        <v>26.37</v>
+        <v>27.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8160</v>
+        <v>18860</v>
       </c>
       <c r="K6" t="n">
-        <v>8070</v>
+        <v>18690</v>
       </c>
       <c r="L6" t="n">
-        <v>8110</v>
+        <v>18760</v>
       </c>
       <c r="M6" t="n">
-        <v>7980</v>
+        <v>18300</v>
       </c>
       <c r="N6" t="n">
-        <v>26.38</v>
+        <v>27.68</v>
       </c>
       <c r="O6" t="n">
-        <v>4827130225</v>
+        <v>13392781755</v>
       </c>
       <c r="P6" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q6" t="n">
-        <v>7980</v>
+        <v>18300</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>LG디스플레이의 FLIP 기술 관련 논의와 미래 전망에 대한 부정적 인식 및 주가 하락 우려.</t>
+          <t>삼성중공업의 LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 조선업 투자 부정적 전망. 뉴스 신뢰도 의문 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FLIP', '기술', '전망']</t>
+          <t>['LNG', 'FLNG', '조선주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1638000</v>
+        <v>7920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.56%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>660</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>406</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>2068</v>
+        <v>206</v>
       </c>
       <c r="H7" t="n">
-        <v>49.52</v>
+        <v>26.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1681000</v>
+        <v>8160</v>
       </c>
       <c r="K7" t="n">
-        <v>1640000</v>
+        <v>8070</v>
       </c>
       <c r="L7" t="n">
-        <v>1653000</v>
+        <v>8110</v>
       </c>
       <c r="M7" t="n">
-        <v>1630000</v>
+        <v>7900</v>
       </c>
       <c r="N7" t="n">
-        <v>49.59</v>
+        <v>26.38</v>
       </c>
       <c r="O7" t="n">
-        <v>1003442654000</v>
+        <v>6908009420</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q7" t="n">
-        <v>403000</v>
+        <v>7900</v>
       </c>
       <c r="R7" t="n">
-        <v>-139000</v>
+        <v>-133000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>로봇용 D램 수요 증가 뉴스에도 불구하고 주가 하락 및 투자자 불만.</t>
+          <t>LG디스플레이의 사업 전망에 대한 부정적 평가와 주가 하락 우려. 일부 기술 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['D램', '로봇', '수요']</t>
+          <t>['FLiPP', 'FMM']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18370</v>
+        <v>1621000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-3.57%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>709</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>431</v>
       </c>
       <c r="G8" t="n">
-        <v>108</v>
+        <v>2160</v>
       </c>
       <c r="H8" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K8" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L8" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M8" t="n">
-        <v>18300</v>
+        <v>1620000</v>
       </c>
       <c r="N8" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O8" t="n">
-        <v>12221549555</v>
+        <v>1147973532500</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>18300</v>
+        <v>403000</v>
       </c>
       <c r="R8" t="n">
-        <v>-1000</v>
+        <v>-139000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성중공업의 수주 소식에도 불구하고 주가 하락 및 신저점 갱신에 대한 불만.</t>
+          <t>로봇용 D램 수요 증가 뉴스에도 불구하고 주가 하락 및 투자자 불만.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '신저점', '조선주']</t>
+          <t>['D램', '로봇', '수요']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16390</v>
+        <v>16160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.6</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H9" t="n">
         <v>3.37</v>
@@ -1248,13 +1248,13 @@
         <v>17400</v>
       </c>
       <c r="M9" t="n">
-        <v>16310</v>
+        <v>16160</v>
       </c>
       <c r="N9" t="n">
         <v>3.97</v>
       </c>
       <c r="O9" t="n">
-        <v>29069382045</v>
+        <v>33532156085</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>광통신 테마 부각 속에서 대한광통신의 주가 상승 기대와 관련 뉴스 언급.</t>
+          <t>대한광통신의 3만원 예상 및 광통신 시장 성장 전망. AI 관련 호재 및 기술적 지지선 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '테마']</t>
+          <t>['광통신', 'AI']</t>
         </is>
       </c>
       <c r="X9" t="n">
